--- a/public/data/campylobacter (1).xlsx
+++ b/public/data/campylobacter (1).xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hawulethundlovu/Documents/Work/gene_Visualizations/public/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADBA932E-09CB-D744-B04F-1C3DA870736D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1C1B2F-C5CB-5841-9309-1BDE4E5BCAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{6498390D-C76C-7347-B667-1AEAAB3E8E14}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="18000" xr2:uid="{6498390D-C76C-7347-B667-1AEAAB3E8E14}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="197">
   <si>
     <t>Gene Name</t>
   </si>
@@ -629,12 +631,210 @@
   <si>
     <t>CmeC is an outer-membrane efflux protein that works only when connected to CmeA and CmeB. Without it,  substrates cannot be expelled into the extracellular space.</t>
   </si>
+  <si>
+    <t>hilA</t>
+  </si>
+  <si>
+    <t>Salmonella typhi</t>
+  </si>
+  <si>
+    <t>NC_003197.2</t>
+  </si>
+  <si>
+    <t>3019846…3021524</t>
+  </si>
+  <si>
+    <t>invasion genes transcription activator</t>
+  </si>
+  <si>
+    <t>NP_461797</t>
+  </si>
+  <si>
+    <t>STM2876</t>
+  </si>
+  <si>
+    <t>activates invasion genes</t>
+  </si>
+  <si>
+    <t>hilD</t>
+  </si>
+  <si>
+    <t>3017838…3018772</t>
+  </si>
+  <si>
+    <t>SPI-1 regulatory cascade activator</t>
+  </si>
+  <si>
+    <t>NP_461796</t>
+  </si>
+  <si>
+    <t>STM2875</t>
+  </si>
+  <si>
+    <t>activates SPI-1 genes required for Salmonella to invade intestinal epithelial cells; upstream regulator that turns on hilA (and the whole invasion cascade).</t>
+  </si>
+  <si>
+    <t>invA</t>
+  </si>
+  <si>
+    <t>3038407…3040471, complement</t>
+  </si>
+  <si>
+    <t>invasion protein</t>
+  </si>
+  <si>
+    <t>NP_461817</t>
+  </si>
+  <si>
+    <t>STM2896</t>
+  </si>
+  <si>
+    <t>encodes an essential structural component of the SPI-1 Type III secretion system that forms part of the secretion apparatus required to inject effector proteins into host cells</t>
+  </si>
+  <si>
+    <t>invF</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>transcriptional activator of invasion protein genes</t>
+  </si>
+  <si>
+    <t>encodes a transcriptional regulator that activates expression of SPI-1 effector genes downstream of hilA, helping drive the production of proteins needed for host cell invasion via the Type III secretion system.</t>
+  </si>
+  <si>
+    <t>sipA</t>
+  </si>
+  <si>
+    <t>actin-binding effector that promotes host cell memebrane shuffling and bacterial uptake</t>
+  </si>
+  <si>
+    <t>binds to host actin, stabilizes cytoskeletal filaments, and protects membrane ruffling to facilitate bacterial uptake, acting downstream of hilD, hilA, and invF.</t>
+  </si>
+  <si>
+    <t>sipC</t>
+  </si>
+  <si>
+    <t>actin-modulating effector and T3SS translocon component that facilitates host cell invasion</t>
+  </si>
+  <si>
+    <t>facilitates bacterial invasion by promoting actin cytoskeleton rearrangement in host cells.</t>
+  </si>
+  <si>
+    <t>ssa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmonella typhi </t>
+  </si>
+  <si>
+    <t>NC_003197</t>
+  </si>
+  <si>
+    <t>1480387…1481886</t>
+  </si>
+  <si>
+    <t>secretion system apparatus protein</t>
+  </si>
+  <si>
+    <t>NP_460359</t>
+  </si>
+  <si>
+    <t>intracellular survival/systemic infection</t>
+  </si>
+  <si>
+    <t>STM1394</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>structural component of the needle complex</t>
+  </si>
+  <si>
+    <t>ssrA</t>
+  </si>
+  <si>
+    <t>secretion system regulator: sensor component</t>
+  </si>
+  <si>
+    <t>part of the ssrA-ssrB two-component regulatory system that "senses" the host intracellular environment and activates transcription of SPI-2 genes.</t>
+  </si>
+  <si>
+    <t>ssrB</t>
+  </si>
+  <si>
+    <t>response regulator of ssrA-ssrB two-component system</t>
+  </si>
+  <si>
+    <t>activates SPI-2 genes (intracellular survival)</t>
+  </si>
+  <si>
+    <t>master regulator of SPI-2</t>
+  </si>
+  <si>
+    <t>sifA</t>
+  </si>
+  <si>
+    <t>SPI-2 effector protein</t>
+  </si>
+  <si>
+    <t>maintains salmonella-containing vacuole (SCV) integrity</t>
+  </si>
+  <si>
+    <t>prevents vacuole rupture; helps intracellular persistence.</t>
+  </si>
+  <si>
+    <t>spiC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blocks phagosome-lysosome fusion </t>
+  </si>
+  <si>
+    <t>modulates host vesicular trafficking; crucial for systemic infection.</t>
+  </si>
+  <si>
+    <t>tviA</t>
+  </si>
+  <si>
+    <t>regulatory protein of VI capsule operon</t>
+  </si>
+  <si>
+    <t>capsule expression  (immune evasion &amp; colonization)</t>
+  </si>
+  <si>
+    <t>controls expression of VI polysaccharide; represses flagella &amp; T3SS-1.</t>
+  </si>
+  <si>
+    <t>tviB-E</t>
+  </si>
+  <si>
+    <t>VI capsule biosynthesis proteins</t>
+  </si>
+  <si>
+    <t>capsule formation (colonization &amp; immune evasion)</t>
+  </si>
+  <si>
+    <t>enzymes for synthesis and export of VI polysaccharide.</t>
+  </si>
+  <si>
+    <t>vexA-E</t>
+  </si>
+  <si>
+    <t>VI capsule export proteins</t>
+  </si>
+  <si>
+    <t>capsule transport (colonization &amp; immune evasion)</t>
+  </si>
+  <si>
+    <t>from export machinery to move Vi polysaccharide to surface</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -755,8 +955,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -775,6 +989,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -785,11 +1004,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -811,9 +1031,11 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1146,6 +1368,1617 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41EDA9A-D777-8341-A704-D29AB4C46BFC}">
+  <dimension ref="A1:P32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="36.33203125" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.1640625" customWidth="1"/>
+    <col min="4" max="4" width="41.83203125" customWidth="1"/>
+    <col min="5" max="6" width="21.83203125" customWidth="1"/>
+    <col min="7" max="8" width="21.5" customWidth="1"/>
+    <col min="9" max="9" width="48.6640625" customWidth="1"/>
+    <col min="10" max="10" width="53.5" customWidth="1"/>
+    <col min="11" max="11" width="143.1640625" customWidth="1"/>
+    <col min="12" max="12" width="36.83203125" customWidth="1"/>
+    <col min="13" max="13" width="32.6640625" customWidth="1"/>
+    <col min="14" max="14" width="37.1640625" customWidth="1"/>
+    <col min="15" max="15" width="35" customWidth="1"/>
+    <col min="16" max="16" width="255.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4">
+        <v>960</v>
+      </c>
+      <c r="F2" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>319</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="4">
+        <v>1413359</v>
+      </c>
+      <c r="O2" s="4">
+        <v>1413910</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="21" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1842</v>
+      </c>
+      <c r="F3" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>613</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="4">
+        <v>583183</v>
+      </c>
+      <c r="O3" s="4">
+        <v>585024</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1833</v>
+      </c>
+      <c r="F4" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>610</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="14">
+        <v>849834</v>
+      </c>
+      <c r="O4" s="14">
+        <v>851666</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="4">
+        <v>807</v>
+      </c>
+      <c r="F5" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>268</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="14">
+        <v>90264</v>
+      </c>
+      <c r="O5" s="4">
+        <v>91070</v>
+      </c>
+      <c r="P5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="4">
+        <v>804</v>
+      </c>
+      <c r="F6" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>267</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="4">
+        <v>1189499</v>
+      </c>
+      <c r="O6" s="4">
+        <v>1190302</v>
+      </c>
+      <c r="P6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="4">
+        <v>798</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>265</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7" s="14">
+        <v>90267</v>
+      </c>
+      <c r="O7" s="14">
+        <v>89470</v>
+      </c>
+      <c r="P7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="21" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="4">
+        <v>570</v>
+      </c>
+      <c r="F8" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>189</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" s="4">
+        <v>88890</v>
+      </c>
+      <c r="O8" s="4">
+        <v>89459</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="4">
+        <v>564</v>
+      </c>
+      <c r="F9" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>187</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="4">
+        <v>1190320</v>
+      </c>
+      <c r="O9" s="4">
+        <v>1190883</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="22" x14ac:dyDescent="0.4">
+      <c r="A10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1719</v>
+      </c>
+      <c r="F10" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>572</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1269232</v>
+      </c>
+      <c r="O10" s="4">
+        <v>1270950</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2175</v>
+      </c>
+      <c r="F11" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>724</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="N11" s="4">
+        <v>817579</v>
+      </c>
+      <c r="O11" s="4">
+        <v>819753</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="4">
+        <v>672</v>
+      </c>
+      <c r="F12" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>223</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="N12" s="4">
+        <v>1191788</v>
+      </c>
+      <c r="O12" s="4">
+        <v>1192459</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="4">
+        <v>723</v>
+      </c>
+      <c r="F13" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>240</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="N13" s="4">
+        <v>1572200</v>
+      </c>
+      <c r="O13" s="4">
+        <v>1572922</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1173</v>
+      </c>
+      <c r="F14" s="4">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>390</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1070252</v>
+      </c>
+      <c r="O14" s="4">
+        <v>1071424</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="4">
+        <v>999</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>332</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="N15" s="4">
+        <v>44287</v>
+      </c>
+      <c r="O15" s="4">
+        <v>45285</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1104</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>367</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="N16" s="4">
+        <v>335718</v>
+      </c>
+      <c r="O16" s="4">
+        <v>336821</v>
+      </c>
+      <c r="P16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="4">
+        <v>3123</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1040</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="N17" s="4">
+        <v>332596</v>
+      </c>
+      <c r="O17" s="4">
+        <v>335718</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1479</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>492</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="N18" s="4">
+        <v>331125</v>
+      </c>
+      <c r="O18" s="4">
+        <v>332603</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19">
+        <v>1679</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>553</v>
+      </c>
+      <c r="I19" t="s">
+        <v>135</v>
+      </c>
+      <c r="J19" t="s">
+        <v>136</v>
+      </c>
+      <c r="K19" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" s="19"/>
+      <c r="M19" t="s">
+        <v>137</v>
+      </c>
+      <c r="N19">
+        <v>3019846</v>
+      </c>
+      <c r="O19">
+        <v>3021524</v>
+      </c>
+      <c r="P19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20">
+        <v>935</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>309</v>
+      </c>
+      <c r="I20" t="s">
+        <v>141</v>
+      </c>
+      <c r="J20" t="s">
+        <v>142</v>
+      </c>
+      <c r="K20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20" s="19"/>
+      <c r="M20" t="s">
+        <v>143</v>
+      </c>
+      <c r="N20">
+        <v>3017838</v>
+      </c>
+      <c r="O20">
+        <v>3018772</v>
+      </c>
+      <c r="P20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21">
+        <v>2065</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>685</v>
+      </c>
+      <c r="I21" t="s">
+        <v>147</v>
+      </c>
+      <c r="J21" t="s">
+        <v>148</v>
+      </c>
+      <c r="K21" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" s="19"/>
+      <c r="M21" t="s">
+        <v>149</v>
+      </c>
+      <c r="N21">
+        <v>3038407</v>
+      </c>
+      <c r="O21">
+        <v>3040471</v>
+      </c>
+      <c r="P21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>216</v>
+      </c>
+      <c r="I22" t="s">
+        <v>153</v>
+      </c>
+      <c r="J22" t="s">
+        <v>152</v>
+      </c>
+      <c r="K22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" s="19"/>
+      <c r="M22" t="s">
+        <v>152</v>
+      </c>
+      <c r="N22" t="s">
+        <v>152</v>
+      </c>
+      <c r="O22" t="s">
+        <v>152</v>
+      </c>
+      <c r="P22" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>450</v>
+      </c>
+      <c r="I23" t="s">
+        <v>156</v>
+      </c>
+      <c r="K23" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" s="19"/>
+      <c r="M23" t="s">
+        <v>152</v>
+      </c>
+      <c r="N23" t="s">
+        <v>152</v>
+      </c>
+      <c r="O23" t="s">
+        <v>152</v>
+      </c>
+      <c r="P23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" t="s">
+        <v>152</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>409</v>
+      </c>
+      <c r="I24" t="s">
+        <v>159</v>
+      </c>
+      <c r="J24" t="s">
+        <v>152</v>
+      </c>
+      <c r="K24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" s="19"/>
+      <c r="M24" t="s">
+        <v>152</v>
+      </c>
+      <c r="N24" t="s">
+        <v>152</v>
+      </c>
+      <c r="O24" t="s">
+        <v>152</v>
+      </c>
+      <c r="P24" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25">
+        <v>1500</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>497</v>
+      </c>
+      <c r="I25" t="s">
+        <v>165</v>
+      </c>
+      <c r="J25" t="s">
+        <v>166</v>
+      </c>
+      <c r="K25" t="s">
+        <v>167</v>
+      </c>
+      <c r="L25" s="19"/>
+      <c r="M25" t="s">
+        <v>168</v>
+      </c>
+      <c r="N25" t="s">
+        <v>152</v>
+      </c>
+      <c r="O25" t="s">
+        <v>169</v>
+      </c>
+      <c r="P25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" t="s">
+        <v>152</v>
+      </c>
+      <c r="E26" t="s">
+        <v>152</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>152</v>
+      </c>
+      <c r="I26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J26" t="s">
+        <v>152</v>
+      </c>
+      <c r="K26" t="s">
+        <v>167</v>
+      </c>
+      <c r="L26" s="19"/>
+      <c r="M26" t="s">
+        <v>152</v>
+      </c>
+      <c r="N26" t="s">
+        <v>152</v>
+      </c>
+      <c r="O26" t="s">
+        <v>152</v>
+      </c>
+      <c r="P26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>152</v>
+      </c>
+      <c r="I27" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" t="s">
+        <v>152</v>
+      </c>
+      <c r="K27" t="s">
+        <v>176</v>
+      </c>
+      <c r="L27" s="19"/>
+      <c r="M27" t="s">
+        <v>152</v>
+      </c>
+      <c r="N27" t="s">
+        <v>152</v>
+      </c>
+      <c r="O27" t="s">
+        <v>152</v>
+      </c>
+      <c r="P27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" t="s">
+        <v>152</v>
+      </c>
+      <c r="D28" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
+        <v>152</v>
+      </c>
+      <c r="I28" t="s">
+        <v>179</v>
+      </c>
+      <c r="J28" t="s">
+        <v>152</v>
+      </c>
+      <c r="K28" t="s">
+        <v>180</v>
+      </c>
+      <c r="L28" s="19"/>
+      <c r="M28" t="s">
+        <v>152</v>
+      </c>
+      <c r="N28" t="s">
+        <v>152</v>
+      </c>
+      <c r="O28" t="s">
+        <v>152</v>
+      </c>
+      <c r="P28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B29" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" t="s">
+        <v>152</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" t="s">
+        <v>152</v>
+      </c>
+      <c r="I29" t="s">
+        <v>179</v>
+      </c>
+      <c r="J29" t="s">
+        <v>152</v>
+      </c>
+      <c r="K29" t="s">
+        <v>183</v>
+      </c>
+      <c r="L29" s="19"/>
+      <c r="M29" t="s">
+        <v>152</v>
+      </c>
+      <c r="N29" t="s">
+        <v>152</v>
+      </c>
+      <c r="O29" t="s">
+        <v>152</v>
+      </c>
+      <c r="P29" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>152</v>
+      </c>
+      <c r="I30" t="s">
+        <v>186</v>
+      </c>
+      <c r="J30" t="s">
+        <v>152</v>
+      </c>
+      <c r="K30" t="s">
+        <v>187</v>
+      </c>
+      <c r="L30" s="19"/>
+      <c r="M30" t="s">
+        <v>152</v>
+      </c>
+      <c r="N30" t="s">
+        <v>152</v>
+      </c>
+      <c r="O30" t="s">
+        <v>152</v>
+      </c>
+      <c r="P30" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A31" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" t="s">
+        <v>162</v>
+      </c>
+      <c r="C31" t="s">
+        <v>152</v>
+      </c>
+      <c r="D31" t="s">
+        <v>152</v>
+      </c>
+      <c r="E31" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="s">
+        <v>152</v>
+      </c>
+      <c r="I31" t="s">
+        <v>190</v>
+      </c>
+      <c r="K31" t="s">
+        <v>191</v>
+      </c>
+      <c r="L31" s="19"/>
+      <c r="M31" t="s">
+        <v>152</v>
+      </c>
+      <c r="N31" t="s">
+        <v>152</v>
+      </c>
+      <c r="O31" t="s">
+        <v>152</v>
+      </c>
+      <c r="P31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" t="s">
+        <v>152</v>
+      </c>
+      <c r="E32" t="s">
+        <v>152</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
+        <v>152</v>
+      </c>
+      <c r="I32" t="s">
+        <v>194</v>
+      </c>
+      <c r="J32" t="s">
+        <v>152</v>
+      </c>
+      <c r="K32" t="s">
+        <v>195</v>
+      </c>
+      <c r="L32" s="19"/>
+      <c r="M32" t="s">
+        <v>152</v>
+      </c>
+      <c r="N32" t="s">
+        <v>152</v>
+      </c>
+      <c r="O32" t="s">
+        <v>152</v>
+      </c>
+      <c r="P32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" display="https://bacteria.ensembl.org/Campylobacter_jejuni_subsp_jejuni_nctc_11168_atcc_700819_gca_000009085/Location/View?db=core;g=Cj1478c;r=Chromosome:1413913-1414872;t=CAL35585" xr:uid="{9B3262D8-C528-9641-BF6F-F7CF3BF1166F}"/>
+    <hyperlink ref="D9" r:id="rId2" display="tel:1190320" xr:uid="{44F0A9C7-92C7-BF45-975B-78BCEA187C94}"/>
+    <hyperlink ref="D10" r:id="rId3" display="tel:1269232" xr:uid="{D1FFE1E9-2F38-AC44-BE99-5317AF08DF09}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B0F44A-31E6-CF4B-A51E-AC669B3077C5}">
   <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2111,13 +3944,20 @@
       <c r="A26" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://bacteria.ensembl.org/Campylobacter_jejuni_subsp_jejuni_nctc_11168_atcc_700819_gca_000009085/Location/View?db=core;g=Cj1478c;r=Chromosome:1413913-1414872;t=CAL35585" xr:uid="{72377CB9-229A-584B-801D-5B2BBF9FE707}"/>
-    <hyperlink ref="D9" r:id="rId2" display="tel:1190320" xr:uid="{E75E3032-C6F1-944A-85D6-54ACFDA4EA09}"/>
-    <hyperlink ref="D10" r:id="rId3" display="tel:1269232" xr:uid="{C9C8B461-2808-5747-94A2-9EAAD96E1BF7}"/>
+    <hyperlink ref="D2" r:id="rId1" display="https://bacteria.ensembl.org/Campylobacter_jejuni_subsp_jejuni_nctc_11168_atcc_700819_gca_000009085/Location/View?db=core;g=Cj1478c;r=Chromosome:1413913-1414872;t=CAL35585" xr:uid="{986ADFBD-94D5-C445-ABFD-F6484A574D97}"/>
+    <hyperlink ref="D9" r:id="rId2" display="tel:1190320" xr:uid="{E0AF8F46-AC7A-7140-AC41-1D96C5A3B25E}"/>
+    <hyperlink ref="D10" r:id="rId3" display="tel:1269232" xr:uid="{917BF606-D486-B746-9552-F9E00BA637D4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70824FAC-31A8-2148-AD0D-FF98CEBF684D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>